--- a/artfynd/A 46709-2021 artfynd.xlsx
+++ b/artfynd/A 46709-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46709-2021 artfynd.xlsx
+++ b/artfynd/A 46709-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15954092</v>
+        <v>54761972</v>
       </c>
       <c r="B2" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221223</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fur rastplats, Bl</t>
+          <t>Fur, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536748.9641721168</v>
+        <v>536795</v>
       </c>
       <c r="R2" t="n">
-        <v>6259082.637373074</v>
+        <v>6259143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Medobs. Gunnar Ohlsson</t>
+          <t>2015-05-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,23 +757,568 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägslänt</t>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Lönnar</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Lönnar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>54761973</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Fur, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>536790</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6259135</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-05-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-05-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Gammal lönn</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gammal lönn</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3529676</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fur, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>536287</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6259184</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2012-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2012-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Medobs. Gunnar Ohlsson</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sjökant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Bengt Nilsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Bengt Nilsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>15951255</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Fur rastplats, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>536793</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6259154</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-05-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Medobs. Gunnar Ohlsson</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15954092</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fur rastplats, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>536749</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6259083</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-05-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Medobs. Gunnar Ohlsson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5776027</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fur, Bl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>536374</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6259245</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sillhövda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-08-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Medobs. Gunnar Ohlsson</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ruderatmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Markväg</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bengt Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46709-2021 artfynd.xlsx
+++ b/artfynd/A 46709-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54761972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54761973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3529676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15951255</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15954092</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5776027</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>